--- a/S_数据表/Pet_Template.xlsx
+++ b/S_数据表/Pet_Template.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11805"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -217,7 +217,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1215" uniqueCount="521">
   <si>
     <t>ID</t>
   </si>
@@ -1773,16 +1773,13 @@
     <t>WuShi</t>
   </si>
   <si>
-    <t>60013011,0.1;60013021,0.1;60013031,0.1;60013041,0.1;60013051,0.1</t>
-  </si>
-  <si>
-    <t>60030106,0.2</t>
+    <t>64009501;64009502;64009503</t>
   </si>
   <si>
     <t>强大法师</t>
   </si>
   <si>
-    <t>60040050,0.2;60040051,0.2</t>
+    <t>60040050;60040051</t>
   </si>
 </sst>
 </file>
@@ -2884,7 +2881,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9">
-    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{80762CD5-88ED-4F35-AEBD-6BB74E0A8F55}">
+    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{60B44DDA-D87A-46F1-BC92-47DC1B69BF3C}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -32479,11 +32476,11 @@
       <c r="AX168" s="12">
         <v>0.5</v>
       </c>
-      <c r="AY168" s="12">
-        <v>0</v>
+      <c r="AY168" s="12" t="s">
+        <v>518</v>
       </c>
       <c r="AZ168" s="15" t="s">
-        <v>518</v>
+        <v>464</v>
       </c>
       <c r="BA168" s="16"/>
       <c r="BB168" s="2"/>
@@ -32860,10 +32857,10 @@
         <v>0.1</v>
       </c>
       <c r="AY169" s="12">
-        <v>0</v>
+        <v>60030106</v>
       </c>
       <c r="AZ169" s="15" t="s">
-        <v>519</v>
+        <v>464</v>
       </c>
       <c r="BA169" s="16"/>
       <c r="BB169" s="2"/>
@@ -33088,7 +33085,7 @@
         <v>70009502</v>
       </c>
       <c r="B170" s="10" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C170" s="11" t="s">
         <v>490</v>
@@ -33239,11 +33236,11 @@
       <c r="AX170" s="12">
         <v>0.1</v>
       </c>
-      <c r="AY170" s="12">
-        <v>0</v>
+      <c r="AY170" s="12" t="s">
+        <v>520</v>
       </c>
       <c r="AZ170" s="15" t="s">
-        <v>521</v>
+        <v>464</v>
       </c>
       <c r="BA170" s="16" t="s">
         <v>487</v>

--- a/S_数据表/Pet_Template.xlsx
+++ b/S_数据表/Pet_Template.xlsx
@@ -217,7 +217,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1215" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="522">
   <si>
     <t>ID</t>
   </si>
@@ -1774,6 +1774,9 @@
   </si>
   <si>
     <t>64009501;64009502;64009503</t>
+  </si>
+  <si>
+    <t>仆从</t>
   </si>
   <si>
     <t>强大法师</t>
@@ -1984,6 +1987,12 @@
     <font>
       <b/>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
       <name val="Tahoma"/>
       <charset val="134"/>
     </font>
@@ -1993,18 +2002,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2881,7 +2884,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9">
-    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{60B44DDA-D87A-46F1-BC92-47DC1B69BF3C}">
+    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{AD98A057-31ED-4084-AEA1-3BDF95E3651D}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -4033,7 +4036,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:JI170"/>
+  <dimension ref="A1:JI171"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11" style="2" customWidth="1"/>
@@ -32702,10 +32705,10 @@
     </row>
     <row r="169" customFormat="1" ht="20.1" customHeight="1" spans="1:269">
       <c r="A169" s="10">
-        <v>70009501</v>
+        <v>70009520</v>
       </c>
       <c r="B169" s="10" t="s">
-        <v>499</v>
+        <v>519</v>
       </c>
       <c r="C169" s="11" t="s">
         <v>496</v>
@@ -32827,7 +32830,7 @@
         <v>1</v>
       </c>
       <c r="AO169" s="12">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="AP169" s="12">
         <v>0</v>
@@ -32856,13 +32859,15 @@
       <c r="AX169" s="12">
         <v>0.1</v>
       </c>
-      <c r="AY169" s="12">
-        <v>60030106</v>
+      <c r="AY169" s="12" t="s">
+        <v>500</v>
       </c>
       <c r="AZ169" s="15" t="s">
         <v>464</v>
       </c>
-      <c r="BA169" s="16"/>
+      <c r="BA169" s="16" t="s">
+        <v>487</v>
+      </c>
       <c r="BB169" s="2"/>
       <c r="BC169" s="2"/>
       <c r="BD169" s="2"/>
@@ -33082,13 +33087,13 @@
     </row>
     <row r="170" customFormat="1" ht="20.1" customHeight="1" spans="1:269">
       <c r="A170" s="10">
-        <v>70009502</v>
+        <v>70009521</v>
       </c>
       <c r="B170" s="10" t="s">
-        <v>519</v>
+        <v>499</v>
       </c>
       <c r="C170" s="11" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="D170" s="10">
         <v>10002</v>
@@ -33161,23 +33166,23 @@
       </c>
       <c r="AA170" s="12">
         <f ca="1">(LOOKUP(W170,$A$2:$A$66,$Z$2:$Z$66)-(AC170+AD170)/2)*Y170*LOOKUP(W170,$A$2:$A$66,$W$2:$W$66)</f>
-        <v>0</v>
+        <v>20420</v>
       </c>
       <c r="AB170" s="12">
         <f ca="1">ROUND(LOOKUP(W170,$A$2:$A$66,Q$2:Q$66)/Z170+(LOOKUP($AE170,$A$2:$A$66,$AA$2:$AA$66)+LOOKUP(W170,$A$2:$A$66,$AB$2:$AB$66))/2,0)</f>
-        <v>0</v>
+        <v>553</v>
       </c>
       <c r="AC170" s="12">
         <f ca="1">ROUND(LOOKUP(X170,$A$2:$A$66,R$2:R$66)/AA170+(LOOKUP($AE170,$A$2:$A$66,$AA$2:$AA$66)+LOOKUP(X170,$A$2:$A$66,$AB$2:$AB$66))/2,0)</f>
-        <v>0</v>
+        <v>553</v>
       </c>
       <c r="AD170" s="12">
         <f ca="1">LOOKUP($AE170,$A:$A,$AA:$AA)</f>
-        <v>0</v>
+        <v>409</v>
       </c>
       <c r="AE170" s="12">
         <f ca="1">LOOKUP($AE170,$A:$A,$AB:$AB)</f>
-        <v>0</v>
+        <v>409</v>
       </c>
       <c r="AF170" s="12">
         <v>0.05</v>
@@ -33236,15 +33241,13 @@
       <c r="AX170" s="12">
         <v>0.1</v>
       </c>
-      <c r="AY170" s="12" t="s">
-        <v>520</v>
+      <c r="AY170" s="12">
+        <v>60030106</v>
       </c>
       <c r="AZ170" s="15" t="s">
         <v>464</v>
       </c>
-      <c r="BA170" s="16" t="s">
-        <v>487</v>
-      </c>
+      <c r="BA170" s="16"/>
       <c r="BB170" s="2"/>
       <c r="BC170" s="2"/>
       <c r="BD170" s="2"/>
@@ -33462,6 +33465,388 @@
       <c r="JH170" s="2"/>
       <c r="JI170" s="2"/>
     </row>
+    <row r="171" customFormat="1" ht="20.1" customHeight="1" spans="1:269">
+      <c r="A171" s="10">
+        <v>70009522</v>
+      </c>
+      <c r="B171" s="10" t="s">
+        <v>520</v>
+      </c>
+      <c r="C171" s="11" t="s">
+        <v>490</v>
+      </c>
+      <c r="D171" s="10">
+        <v>10002</v>
+      </c>
+      <c r="E171" s="10">
+        <v>50000001</v>
+      </c>
+      <c r="F171" s="10">
+        <v>0</v>
+      </c>
+      <c r="G171" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="H171" s="12">
+        <v>0</v>
+      </c>
+      <c r="I171" s="12">
+        <v>1</v>
+      </c>
+      <c r="J171" s="10">
+        <v>28</v>
+      </c>
+      <c r="K171" s="10">
+        <v>0</v>
+      </c>
+      <c r="L171" s="10">
+        <v>2</v>
+      </c>
+      <c r="M171" s="12">
+        <v>3888</v>
+      </c>
+      <c r="N171" s="12">
+        <v>5184</v>
+      </c>
+      <c r="O171" s="12">
+        <v>1037</v>
+      </c>
+      <c r="P171" s="12">
+        <v>1382</v>
+      </c>
+      <c r="Q171" s="12">
+        <v>1426</v>
+      </c>
+      <c r="R171" s="12">
+        <v>1901</v>
+      </c>
+      <c r="S171" s="12">
+        <v>1426</v>
+      </c>
+      <c r="T171" s="12">
+        <v>1600</v>
+      </c>
+      <c r="U171" s="12">
+        <v>1296</v>
+      </c>
+      <c r="V171" s="12">
+        <v>1600</v>
+      </c>
+      <c r="W171" s="12">
+        <v>3000</v>
+      </c>
+      <c r="X171" s="12">
+        <v>3000</v>
+      </c>
+      <c r="Y171" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z171" s="12">
+        <v>1.5</v>
+      </c>
+      <c r="AA171" s="12">
+        <f ca="1">(LOOKUP(W171,$A$2:$A$66,$Z$2:$Z$66)-(AC171+AD171)/2)*Y171*LOOKUP(W171,$A$2:$A$66,$W$2:$W$66)</f>
+        <v>0</v>
+      </c>
+      <c r="AB171" s="12">
+        <f ca="1">ROUND(LOOKUP(W171,$A$2:$A$66,Q$2:Q$66)/Z171+(LOOKUP($AE171,$A$2:$A$66,$AA$2:$AA$66)+LOOKUP(W171,$A$2:$A$66,$AB$2:$AB$66))/2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AC171" s="12">
+        <f ca="1">ROUND(LOOKUP(X171,$A$2:$A$66,R$2:R$66)/AA171+(LOOKUP($AE171,$A$2:$A$66,$AA$2:$AA$66)+LOOKUP(X171,$A$2:$A$66,$AB$2:$AB$66))/2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD171" s="12">
+        <f ca="1">LOOKUP($AE171,$A:$A,$AA:$AA)</f>
+        <v>0</v>
+      </c>
+      <c r="AE171" s="12">
+        <f ca="1">LOOKUP($AE171,$A:$A,$AB:$AB)</f>
+        <v>0</v>
+      </c>
+      <c r="AF171" s="12">
+        <v>0.05</v>
+      </c>
+      <c r="AG171" s="12">
+        <v>0</v>
+      </c>
+      <c r="AH171" s="12">
+        <v>0.75</v>
+      </c>
+      <c r="AI171" s="12">
+        <v>0.05</v>
+      </c>
+      <c r="AJ171" s="12">
+        <v>0</v>
+      </c>
+      <c r="AK171" s="12">
+        <v>0</v>
+      </c>
+      <c r="AL171" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM171" s="12">
+        <v>6</v>
+      </c>
+      <c r="AN171" s="12">
+        <v>1</v>
+      </c>
+      <c r="AO171" s="12">
+        <v>6</v>
+      </c>
+      <c r="AP171" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ171" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR171" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS171" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT171" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU171" s="12">
+        <v>3</v>
+      </c>
+      <c r="AV171" s="12">
+        <v>10</v>
+      </c>
+      <c r="AW171" s="12">
+        <v>15</v>
+      </c>
+      <c r="AX171" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="AY171" s="12" t="s">
+        <v>521</v>
+      </c>
+      <c r="AZ171" s="15" t="s">
+        <v>464</v>
+      </c>
+      <c r="BA171" s="16" t="s">
+        <v>487</v>
+      </c>
+      <c r="BB171" s="2"/>
+      <c r="BC171" s="2"/>
+      <c r="BD171" s="2"/>
+      <c r="BE171" s="2"/>
+      <c r="BF171" s="2"/>
+      <c r="BG171" s="2"/>
+      <c r="BH171" s="2"/>
+      <c r="BI171" s="2"/>
+      <c r="BJ171" s="2"/>
+      <c r="BK171" s="2"/>
+      <c r="BL171" s="2"/>
+      <c r="BM171" s="2"/>
+      <c r="BN171" s="2"/>
+      <c r="BO171" s="2"/>
+      <c r="BP171" s="2"/>
+      <c r="BQ171" s="2"/>
+      <c r="BR171" s="2"/>
+      <c r="BS171" s="2"/>
+      <c r="BT171" s="2"/>
+      <c r="BU171" s="2"/>
+      <c r="BV171" s="2"/>
+      <c r="BW171" s="2"/>
+      <c r="BX171" s="2"/>
+      <c r="BY171" s="2"/>
+      <c r="BZ171" s="2"/>
+      <c r="CA171" s="2"/>
+      <c r="CB171" s="2"/>
+      <c r="CC171" s="2"/>
+      <c r="CD171" s="2"/>
+      <c r="CE171" s="2"/>
+      <c r="CF171" s="2"/>
+      <c r="CG171" s="2"/>
+      <c r="CH171" s="2"/>
+      <c r="CI171" s="2"/>
+      <c r="CJ171" s="2"/>
+      <c r="CK171" s="2"/>
+      <c r="CL171" s="2"/>
+      <c r="CM171" s="2"/>
+      <c r="CN171" s="2"/>
+      <c r="CO171" s="2"/>
+      <c r="CP171" s="2"/>
+      <c r="CQ171" s="2"/>
+      <c r="CR171" s="2"/>
+      <c r="CS171" s="2"/>
+      <c r="CT171" s="2"/>
+      <c r="CU171" s="2"/>
+      <c r="CV171" s="2"/>
+      <c r="CW171" s="2"/>
+      <c r="CX171" s="2"/>
+      <c r="CY171" s="2"/>
+      <c r="CZ171" s="2"/>
+      <c r="DA171" s="2"/>
+      <c r="DB171" s="2"/>
+      <c r="DC171" s="2"/>
+      <c r="DD171" s="2"/>
+      <c r="DE171" s="2"/>
+      <c r="DF171" s="2"/>
+      <c r="DG171" s="2"/>
+      <c r="DH171" s="2"/>
+      <c r="DI171" s="2"/>
+      <c r="DJ171" s="2"/>
+      <c r="DK171" s="2"/>
+      <c r="DL171" s="2"/>
+      <c r="DM171" s="2"/>
+      <c r="DN171" s="2"/>
+      <c r="DO171" s="2"/>
+      <c r="DP171" s="2"/>
+      <c r="DQ171" s="2"/>
+      <c r="DR171" s="2"/>
+      <c r="DS171" s="2"/>
+      <c r="DT171" s="2"/>
+      <c r="DU171" s="2"/>
+      <c r="DV171" s="2"/>
+      <c r="DW171" s="2"/>
+      <c r="DX171" s="2"/>
+      <c r="DY171" s="2"/>
+      <c r="DZ171" s="2"/>
+      <c r="EA171" s="2"/>
+      <c r="EB171" s="2"/>
+      <c r="EC171" s="2"/>
+      <c r="ED171" s="2"/>
+      <c r="EE171" s="2"/>
+      <c r="EF171" s="2"/>
+      <c r="EG171" s="2"/>
+      <c r="EH171" s="2"/>
+      <c r="EI171" s="2"/>
+      <c r="EJ171" s="2"/>
+      <c r="EK171" s="2"/>
+      <c r="EL171" s="2"/>
+      <c r="EM171" s="2"/>
+      <c r="EN171" s="2"/>
+      <c r="EO171" s="2"/>
+      <c r="EP171" s="2"/>
+      <c r="EQ171" s="2"/>
+      <c r="ER171" s="2"/>
+      <c r="ES171" s="2"/>
+      <c r="ET171" s="2"/>
+      <c r="EU171" s="2"/>
+      <c r="EV171" s="2"/>
+      <c r="EW171" s="2"/>
+      <c r="EX171" s="2"/>
+      <c r="EY171" s="2"/>
+      <c r="EZ171" s="2"/>
+      <c r="FA171" s="2"/>
+      <c r="FB171" s="2"/>
+      <c r="FC171" s="2"/>
+      <c r="FD171" s="2"/>
+      <c r="FE171" s="2"/>
+      <c r="FF171" s="2"/>
+      <c r="FG171" s="2"/>
+      <c r="FH171" s="2"/>
+      <c r="FI171" s="2"/>
+      <c r="FJ171" s="2"/>
+      <c r="FK171" s="2"/>
+      <c r="FL171" s="2"/>
+      <c r="FM171" s="2"/>
+      <c r="FN171" s="2"/>
+      <c r="FO171" s="2"/>
+      <c r="FP171" s="2"/>
+      <c r="FQ171" s="2"/>
+      <c r="FR171" s="2"/>
+      <c r="FS171" s="2"/>
+      <c r="FT171" s="2"/>
+      <c r="FU171" s="2"/>
+      <c r="FV171" s="2"/>
+      <c r="FW171" s="2"/>
+      <c r="FX171" s="2"/>
+      <c r="FY171" s="2"/>
+      <c r="FZ171" s="2"/>
+      <c r="GA171" s="2"/>
+      <c r="GB171" s="2"/>
+      <c r="GC171" s="2"/>
+      <c r="GD171" s="2"/>
+      <c r="GE171" s="2"/>
+      <c r="GF171" s="2"/>
+      <c r="GG171" s="2"/>
+      <c r="GH171" s="2"/>
+      <c r="GI171" s="2"/>
+      <c r="GJ171" s="2"/>
+      <c r="GK171" s="2"/>
+      <c r="GL171" s="2"/>
+      <c r="GM171" s="2"/>
+      <c r="GN171" s="2"/>
+      <c r="GO171" s="2"/>
+      <c r="GP171" s="2"/>
+      <c r="GQ171" s="2"/>
+      <c r="GR171" s="2"/>
+      <c r="GS171" s="2"/>
+      <c r="GT171" s="2"/>
+      <c r="GU171" s="2"/>
+      <c r="GV171" s="2"/>
+      <c r="GW171" s="2"/>
+      <c r="GX171" s="2"/>
+      <c r="GY171" s="2"/>
+      <c r="GZ171" s="2"/>
+      <c r="HA171" s="2"/>
+      <c r="HB171" s="2"/>
+      <c r="HC171" s="2"/>
+      <c r="HD171" s="2"/>
+      <c r="HE171" s="2"/>
+      <c r="HF171" s="2"/>
+      <c r="HG171" s="2"/>
+      <c r="HH171" s="2"/>
+      <c r="HI171" s="2"/>
+      <c r="HJ171" s="2"/>
+      <c r="HK171" s="2"/>
+      <c r="HL171" s="2"/>
+      <c r="HM171" s="2"/>
+      <c r="HN171" s="2"/>
+      <c r="HO171" s="2"/>
+      <c r="HP171" s="2"/>
+      <c r="HQ171" s="2"/>
+      <c r="HR171" s="2"/>
+      <c r="HS171" s="2"/>
+      <c r="HT171" s="2"/>
+      <c r="HU171" s="2"/>
+      <c r="HV171" s="2"/>
+      <c r="HW171" s="2"/>
+      <c r="HX171" s="2"/>
+      <c r="HY171" s="2"/>
+      <c r="HZ171" s="2"/>
+      <c r="IA171" s="2"/>
+      <c r="IB171" s="2"/>
+      <c r="IC171" s="2"/>
+      <c r="ID171" s="2"/>
+      <c r="IE171" s="2"/>
+      <c r="IF171" s="2"/>
+      <c r="IG171" s="2"/>
+      <c r="IH171" s="2"/>
+      <c r="II171" s="2"/>
+      <c r="IJ171" s="2"/>
+      <c r="IK171" s="2"/>
+      <c r="IL171" s="2"/>
+      <c r="IM171" s="2"/>
+      <c r="IN171" s="2"/>
+      <c r="IO171" s="2"/>
+      <c r="IP171" s="2"/>
+      <c r="IQ171" s="2"/>
+      <c r="IR171" s="2"/>
+      <c r="IS171" s="2"/>
+      <c r="IT171" s="2"/>
+      <c r="IU171" s="2"/>
+      <c r="IV171" s="2"/>
+      <c r="IW171" s="2"/>
+      <c r="IX171" s="2"/>
+      <c r="IY171" s="2"/>
+      <c r="IZ171" s="2"/>
+      <c r="JA171" s="2"/>
+      <c r="JB171" s="2"/>
+      <c r="JC171" s="2"/>
+      <c r="JD171" s="2"/>
+      <c r="JE171" s="2"/>
+      <c r="JF171" s="2"/>
+      <c r="JG171" s="2"/>
+      <c r="JH171" s="2"/>
+      <c r="JI171" s="2"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C8" r:id="rId3" display="Timber Wolf"/>

--- a/S_数据表/Pet_Template.xlsx
+++ b/S_数据表/Pet_Template.xlsx
@@ -217,7 +217,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1221" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="522">
   <si>
     <t>ID</t>
   </si>
@@ -1985,7 +1985,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2002,14 +2001,15 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -2884,7 +2884,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9">
-    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{AD98A057-31ED-4084-AEA1-3BDF95E3651D}">
+    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{333911E2-099B-4C07-ADF1-9F8C8D541123}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -32859,8 +32859,8 @@
       <c r="AX169" s="12">
         <v>0.1</v>
       </c>
-      <c r="AY169" s="12" t="s">
-        <v>500</v>
+      <c r="AY169" s="12">
+        <v>0</v>
       </c>
       <c r="AZ169" s="15" t="s">
         <v>464</v>
